--- a/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_coquimbo.xlsx
+++ b/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_coquimbo.xlsx
@@ -410,7 +410,7 @@
         <v>111.2849377220391</v>
       </c>
       <c r="C3">
-        <v>17.61629901637367</v>
+        <v>17.61629901637366</v>
       </c>
       <c r="D3">
         <v>62.77941359432671</v>
@@ -435,7 +435,7 @@
         <v>59.54325468844525</v>
       </c>
       <c r="E4">
-        <v>23.58590441621295</v>
+        <v>23.58590441621294</v>
       </c>
     </row>
     <row r="5">
@@ -489,7 +489,7 @@
         <v>16.11126411456899</v>
       </c>
       <c r="D7">
-        <v>61.61143241837266</v>
+        <v>61.61143241837267</v>
       </c>
       <c r="E7">
         <v>22.27730346705836</v>
@@ -508,7 +508,7 @@
         <v>16.36928289102202</v>
       </c>
       <c r="D8">
-        <v>60.12422360248447</v>
+        <v>60.12422360248446</v>
       </c>
       <c r="E8">
         <v>23.50649350649351</v>
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="B13">
-        <v>213.1591448931116</v>
+        <v>213.1591448931117</v>
       </c>
       <c r="C13">
         <v>12.96821094135042</v>
       </c>
       <c r="D13">
-        <v>59.38886150813209</v>
+        <v>59.38886150813208</v>
       </c>
       <c r="E13">
         <v>27.64292755051749</v>
@@ -622,10 +622,10 @@
         <v>16.75095005835004</v>
       </c>
       <c r="D14">
-        <v>60.6451419850983</v>
+        <v>60.64514198509831</v>
       </c>
       <c r="E14">
-        <v>22.60390795655166</v>
+        <v>22.60390795655167</v>
       </c>
     </row>
     <row r="15">
@@ -641,7 +641,7 @@
         <v>15.92067593045178</v>
       </c>
       <c r="D15">
-        <v>60.03770686404581</v>
+        <v>60.0377068640458</v>
       </c>
       <c r="E15">
         <v>24.04161720550241</v>
